--- a/weekly_temp/patents_超导量子测控技术.xlsx
+++ b/weekly_temp/patents_超导量子测控技术.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>量子计算控制装置、量子计算机及量子计算控制方法</t>
+          <t>用于量子位读出器的补偿脉冲</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>独立行政法人科学技术振兴机构</t>
+          <t>谷歌有限责任公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>中村泰信 | 田渊丰 | 玉手修平</t>
+          <t>KELLY, JULIAN SHAW | SANK, DANIEL THOMAS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,34 +476,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>量子计算控制装置具备控制信号生成部和量子比特模块。量子比特模块具备观测部、量子比特基板部、控制电路部、观测电路部以及信号处理电路部。多个量子比特分组为由各量子比特彼此的位置关系相同的多个量子比特构成的多个组而配置在量子比特基板部上。控制信号生成部生成控制信号和命令信号，控制信号用于执行一个以上的种类的空间上均匀的第一操作及以比一个以上的种类的第一操作低的频度来进行的空间上不均匀的第二操作，命令信号用于使控制电路部执行第一操作及第二操作的控制，该第一操作及第二操作是针对量子比特基板部上的量子比特的操作。控制电路部将控制信号分支到组，根据命令信号，对控制信号向量子比特基板部上的各量子比特的送出进行控制。观测电路部观测接受了第一操作或第二操作的各量子比特的状态。信号处理电路部向观测部发送各量子比特的观测信号。</t>
+          <t>用于执行量子比特读出的装置和方法。在一个方面,该装置包括:一个以量子比特频率运行的量子比特;一个频率控制器,该频率控制器被配置为控制量子比特频率,并且在量子比特测量操作期间被配置为:确定一个补偿脉冲,该补偿脉冲施加到量子比特时,可以抵消量子比特测量操作期间的量子比特频率变化;以及在量子比特测量操作期间将所确定的补偿脉冲施加到量子比特,以维持量子比特频率。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=efec951d-1740-473f-842d-97180ce3a76d&amp;shareId=6C954144-4337-8587-B920-0768CD63F0BC&amp;from=EXPORT&amp;signature=dYIEs3T9XCCvAhnMPXglbsQkg5W3ylQrulIAXZOT%2FUo%3D&amp;expire=94608000&amp;date=20260529T004936Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=f523a155-4124-4cb1-869d-65ee92a90464&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=Qf10HAnxMoxjgeigLmmNQknQXHN%2FOyApPqsPEsFwyr8%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>用于量子计算测控的集成滤波放大装置</t>
+          <t>用于读取和解码量子信息的设备</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>相干(北京)科技有限公司</t>
+          <t>原子能和替代能源委员会</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>赵剑琴 | 邢磊 | 田建强 | 贺玉龙 | 曾祥洪</t>
+          <t>SCHMIDT, QUENTIN | BADETS, FRANCK | THONNART, YVAIN | JADOT, BAPTISTE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,17 +513,242 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本申请涉及一种用于量子计算测控的集成滤波放大装置，包括：装置壳体、电路板、前端衰减组件、前端带通滤波组件、微波放大组件、后端衰减组件和后端带通滤波组件，前端带通滤波组件、前端衰减组件、微波放大组件、后端衰减组件和后端带通滤波组件，依次连接设置在所述电路板上，且均集成在装置壳体内，通过集成带通滤波器、衰减器和微波放大器的微波前端模块，极大降低了外部线路复杂性，且该集成前端模块体积小，可直接集成到电子学设备中，使得测控脉冲从电子学设备中发生后可直接接入稀释制冷机内，极大简化了外部接线，提升了系统可靠性。</t>
+          <t>本发明涉及一种量子器件,其包括多个量子比特(11、12、…、1M、21…)、一个解复用电路、一条用于将来自所述量子比特的读取信号传输至所述解复用电路的公共传输线,以及针对每个量子比特的量子静电计(S11、S12、…、S1M、S21…),用于在所述公共传输线上传输一个信号,该信号是所述量子比特当前状态和施加于所述量子静电计的周期性激励的函数。该量子器件的独特之处在于,传输至器件中一组量子比特的周期性激励以相同的频率传输。该器件包括用于引入不同相移(Φ1、Φ2、…、ΦM)的移相装置,以及可选的用于在施加于各个量子静电计的激励中引入幅度差异的幅度衰减装置。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=02fd591a-9387-4d8e-abef-42688565ec39&amp;shareId=6C954144-4337-8587-B920-0768CD63F0BC&amp;from=EXPORT&amp;signature=o8BgqBf3yBIRJJYUR5GH25TkOpR%2Fuijj3EBJGYBnqCE%3D&amp;expire=94608000&amp;date=20260529T004936Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=dde063dd-d9a6-4ba7-ba5b-e50fd97c313c&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=FmV3cEjTPWu%2BS3YzV%2F6OtaXvVUwRIAfWSPJiE2n1nwQ%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>一种在超导量子系统中实现混合维度量子相位门的方法</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>张钰 | 于扬</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>本发明属于超导量子计算技术领域，涉及一种在超导量子系统中实现混合维度量子相位门的方法，系统包括：微波腔作为用于承载光子并编码目标量子比特的量子谐振器；超导磁通三能级量子比特作为用作控制位的三能级量子系统，通过电容与微波腔耦合；经典微波脉冲源用于将产生的可控微波驱动场施加于超导磁通三能级量子比特；实现方法是利用超导量子系统中的超导磁通三能级量子比特与微波腔之间的色散耦合作用，并结合施加于超导磁通三能级量子比特的可控微波驱动场，通过一步演化过程，确定性地实现超导磁通三能级量子比特量子态对腔场相位的条件控制；本发明成功率100%，操作可靠性远优于概率性的光学方案。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=7858d0b7-432f-4508-88e8-e2c3c79fa3f8&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=d0zbxvENPo7C5oj%2FExdIlONDaC7ftusA8TqhfIF5LDQ%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>用于调谐量子计算机的至少两个量子比特之间的相互作用强度的方法和量子计算机</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>伊莱克特伦有限公司</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>帕特里克·胡贝尔 | 克里斯托夫·文德利希</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>本文中具体说明了用于调谐量子计算机（10）的至少两个量子比特（qb1，qb2）之间的相互作用强度（J）的方法，该方法包括以下步骤：‑ 将第一周期性脉冲序列（1）施加至第一量子比特（qb1），‑ 将第二周期性脉冲序列（2）施加至第二量子比特（qb2），其中，‑ 第一周期性脉冲序列（1）的周期（T）等于第二周期性脉冲序列（2）的周期（T），‑ 使第二周期性脉冲序列（2）的脉冲（21）相对于第一周期性脉冲序列（1）的脉冲（11）时间延迟，以及‑ 通过控制所述时间延迟（Δt）来调谐相互作用强度（J）。此外，本文中具体说明了量子计算机（10）。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=07a01fc7-1d61-4183-8bd9-b8979bafff6a&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=i9Y4JWZuYTtlsPTUZs84Pd3SQr4qxO3lvUqa%2FIwd2A0%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>用于超导量子比特的非绝热单磁通量子(SFQ)读出的量子计算系统</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>芯科量子公司</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>アレッサンドロ ミアノ | オレグ ムカノフ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>本发明提供一种计算或信息处理系统,该系统包括量子计算模块,该量子计算模块利用量子力学器件或电路的量子态执行信息处理或计算。 
+ 【解决方案】该计算或信息处理系统采用基于超导的量子计算模块(例如,超导约瑟夫森结),并构建量子计算模块或器件以及经典数字计算模块或器件,用于各种基于量子计算的应用。此类量子系统包含基于超导约瑟夫森结的量子比特集合,并基于量子比特量子态的叠加和关联/纠缠执行复杂的计算。量子比特器件由量子比特控制电路控制,量子比特读出电路在量子比特控制电路的控制下测量量子比特器件的量子态,并根据测量结果提供量子比特读出。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=88ad0e44-80d4-439c-b505-c7a5d8291a92&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=G9LfKTB8JnqoRI2Dn8R4dRfNs%2F2jOb1qytdxeOVTk6c%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>超导量子处理电路中的可调谐量子比特器件</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RIGETTI &amp; CO INC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SETE, EYOB A. | CHEN, ANGELA Q. | POLETTO, STEFANO | KULSHRESHTHA, SHOBHAN | MANENTI, RICCARDO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>一般而言,超导量子处理电路包含一个可调谐量子比特器件。该可调谐量子比特器件包含一个电路环路,该电路环路配置成在可调谐量子比特器件工作期间接收磁通量,该磁通量控制该可调谐量子比特器件的量子比特频率。在一些实施例中,该电路环路由以下部分组成:一个非线性电路元件和一个或多个线性电路元件。该单个非线性电路元件是连接在第一电路节点和第二电路节点之间的约瑟夫森结。该一个或多个线性电路元件包括一个与连接在第一电路节点和第二电路节点之间的约瑟夫森结并联的线性电感器。</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=7ee4ebb7-bf1f-4709-9bd8-e2c11c904371&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=113QyBsuqSB7ew5nF5t9X7v8ckZq86qN%2FYBOiHEoKcY%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>带有嵌入式读出的紧凑型硅量子比特单元</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>量子运动科技有限公司</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GONZALEZ-ZALBA, MIGUEL FERNANDO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>本发明公开了一种量子器件,该器件具有用于执行量子比特测量或读出的LC谐振器电路。该器件包括硅层( 601 ),介电层( 603 ) 布置在硅层上并与硅层形成功能界面( 601 ),第一金属区( 614 )布置在介电层上603以及第二个金属区域( 624 )布置在介电层上603并与第一金属区域横向分离( 614第一和第二金属区( 614, 624 )被布置成电连接,使得可以在第一和第二金属区域下方感应出一个双量子点,形成一个具有第一态和第二态的量子比特( 614, 624在功能界面处。双量子点提供了一个电容 C 1在LC谐振器电路中,双量子点的电容取决于量子比特的状态。第一个金属区域( 614 ) 提供一个电感器 L 1在 LC 谐振器电路中,LC 谐振器电路的谐振频率取决于量子比特的状态,因此可以测量或推断量子比特的状态。</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=c4572404-b8ad-47b4-9a02-11d0d900b01a&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=hfKywHVMw%2BVdoUO9gdOfjExUoagn07uL2GPrjy0yOIY%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>用于量子计算误差抑制的分层噪声自适应控制系统及方法</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IEN ARCHITECT OFFICE CO LTD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>정찬희</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>本发明涉及一种用于减少量子计算环境中物理误差的分层控制系统和方法。本发明利用包含室温控制代理(RTAA)和近端硬件控制器(NHC)的双层控制结构,实现了实时脉冲控制和自适应噪声参数更新的并行执行。 
+具体而言,本发明包括:(1) 噪声不对称反向镜像 (NAEM),用于反转超导量子比特 T1 弛豫方向的不对称性;(2) 节律频谱指纹识别 (RSF),通过对门脉冲施加周期性调制,为解码器输入提供结构特征量;(3) 经典顺序引导序列化 (CGS),用作辅助元数据通道,用于检测经典控制通道的顺序计数器异常;以及 (4) 分层自适应控制 (HAC),用于分离室温控制代理和近端硬件控制器的角色。 
+本发明涉及一种在保持现有电路功能结构的同时自适应地优化执行控制参数的技术,而对电路结构本身的改变,例如逻辑量子比特和物理量子比特之间的重新映射、重新排列门执行顺序或重新配置电路深度,并非本发明的直接主题。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=4e488ee2-feac-4374-af22-02ceaaf24a98&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=n1OpBWABvcgiGtIaeCREOf1jZGqGWQc8e7CdYxtG6Mg%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_超导量子测控技术.xlsx
+++ b/weekly_temp/patents_超导量子测控技术.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>用于量子位读出器的补偿脉冲</t>
+          <t>用于量子数据查找的电路设计</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>谷歌有限责任公司</t>
+          <t>微软技术许可有限责任公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KELLY, JULIAN SHAW | SANK, DANIEL THOMAS</t>
+          <t>SUNDARAM, AARTHI MEENAKSHI | ZHU, SHUCHEN | LOW, GUANG HAO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,279 +476,54 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>用于执行量子比特读出的装置和方法。在一个方面,该装置包括:一个以量子比特频率运行的量子比特;一个频率控制器,该频率控制器被配置为控制量子比特频率,并且在量子比特测量操作期间被配置为:确定一个补偿脉冲,该补偿脉冲施加到量子比特时,可以抵消量子比特测量操作期间的量子比特频率变化;以及在量子比特测量操作期间将所确定的补偿脉冲施加到量子比特,以维持量子比特频率。</t>
+          <t>本公开的方面包括一种量子查找技术。这些方面包括:响应于接收输入,将输入路由通过第一量子路由器以确定第一输出。这些方面包括:将第一输出路由到至少一个第二量子路由器,该至少一个第二量子路由器将第一输出馈送到门树,该门树生成第二输出,该第二输出被馈送到量子位,量子位执行操作并生成读出。这些方面包括:将读出路由通过第三量子路由器,该第三量子路由器被布置用于输出读出。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=f523a155-4124-4cb1-869d-65ee92a90464&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=Qf10HAnxMoxjgeigLmmNQknQXHN%2FOyApPqsPEsFwyr8%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=b499c2e1-f153-4f19-a7e8-6ee31a3a32cf&amp;shareId=4G0297G6-613E-5D50-0F19-1180B5GF30B6&amp;from=EXPORT&amp;signature=FjmTR%2Ftxl92ABHSVId64caGwZfwno5i3ahDj%2FpWgmLQ%3D&amp;expire=94608000&amp;date=20260626T004457Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>用于读取和解码量子信息的设备</t>
+          <t>使用超导刚挠电路支持量子位平面与量子位平面的控制系统之间的高热梯度的系统和方法</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>原子能和替代能源委员会</t>
+          <t>微软技术许可有限责任公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SCHMIDT, QUENTIN | BADETS, FRANCK | THONNART, YVAIN | JADOT, BAPTISTE</t>
+          <t>TURNER, MATTHEW DAVID | RANTA, CRAIG STEVEN | KRAMER, KEVIN JAMES</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本发明涉及一种量子器件,其包括多个量子比特(11、12、…、1M、21…)、一个解复用电路、一条用于将来自所述量子比特的读取信号传输至所述解复用电路的公共传输线,以及针对每个量子比特的量子静电计(S11、S12、…、S1M、S21…),用于在所述公共传输线上传输一个信号,该信号是所述量子比特当前状态和施加于所述量子静电计的周期性激励的函数。该量子器件的独特之处在于,传输至器件中一组量子比特的周期性激励以相同的频率传输。该器件包括用于引入不同相移(Φ1、Φ2、…、ΦM)的移相装置,以及可选的用于在施加于各个量子静电计的激励中引入幅度差异的幅度衰减装置。</t>
+          <t>本文描述了用于在量子比特平面和该量子比特平面的控制系统之间维持高温度梯度的系统和方法。该系统包括与超导刚挠性电路的第一刚性电路部分关联的量子比特平面,以及与该超导刚挠性电路的第二刚性电路部分关联的控制系统。该超导刚挠性电路包括用于连接第一刚性电路部分和第二刚性电路部分的柔性电路部分。该系统还包括第一冷却系统,用于将量子比特平面和超导刚挠性电路的第一刚性电路部分的工作温度维持在100毫开尔文或以下。该系统还包括第二冷却系统,用于将控制系统和超导刚挠性电路的第二刚性电路部分的工作温度维持在10开尔文或以下。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=dde063dd-d9a6-4ba7-ba5b-e50fd97c313c&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=FmV3cEjTPWu%2BS3YzV%2F6OtaXvVUwRIAfWSPJiE2n1nwQ%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>一种在超导量子系统中实现混合维度量子相位门的方法</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>南京大学</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>张钰 | 于扬</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>本发明属于超导量子计算技术领域，涉及一种在超导量子系统中实现混合维度量子相位门的方法，系统包括：微波腔作为用于承载光子并编码目标量子比特的量子谐振器；超导磁通三能级量子比特作为用作控制位的三能级量子系统，通过电容与微波腔耦合；经典微波脉冲源用于将产生的可控微波驱动场施加于超导磁通三能级量子比特；实现方法是利用超导量子系统中的超导磁通三能级量子比特与微波腔之间的色散耦合作用，并结合施加于超导磁通三能级量子比特的可控微波驱动场，通过一步演化过程，确定性地实现超导磁通三能级量子比特量子态对腔场相位的条件控制；本发明成功率100%，操作可靠性远优于概率性的光学方案。</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=7858d0b7-432f-4508-88e8-e2c3c79fa3f8&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=d0zbxvENPo7C5oj%2FExdIlONDaC7ftusA8TqhfIF5LDQ%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>用于调谐量子计算机的至少两个量子比特之间的相互作用强度的方法和量子计算机</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>伊莱克特伦有限公司</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>帕特里克·胡贝尔 | 克里斯托夫·文德利希</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>本文中具体说明了用于调谐量子计算机（10）的至少两个量子比特（qb1，qb2）之间的相互作用强度（J）的方法，该方法包括以下步骤：‑ 将第一周期性脉冲序列（1）施加至第一量子比特（qb1），‑ 将第二周期性脉冲序列（2）施加至第二量子比特（qb2），其中，‑ 第一周期性脉冲序列（1）的周期（T）等于第二周期性脉冲序列（2）的周期（T），‑ 使第二周期性脉冲序列（2）的脉冲（21）相对于第一周期性脉冲序列（1）的脉冲（11）时间延迟，以及‑ 通过控制所述时间延迟（Δt）来调谐相互作用强度（J）。此外，本文中具体说明了量子计算机（10）。</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=07a01fc7-1d61-4183-8bd9-b8979bafff6a&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=i9Y4JWZuYTtlsPTUZs84Pd3SQr4qxO3lvUqa%2FIwd2A0%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>用于超导量子比特的非绝热单磁通量子(SFQ)读出的量子计算系统</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>芯科量子公司</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>アレッサンドロ ミアノ | オレグ ムカノフ</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>本发明提供一种计算或信息处理系统,该系统包括量子计算模块,该量子计算模块利用量子力学器件或电路的量子态执行信息处理或计算。 
- 【解决方案】该计算或信息处理系统采用基于超导的量子计算模块(例如,超导约瑟夫森结),并构建量子计算模块或器件以及经典数字计算模块或器件,用于各种基于量子计算的应用。此类量子系统包含基于超导约瑟夫森结的量子比特集合,并基于量子比特量子态的叠加和关联/纠缠执行复杂的计算。量子比特器件由量子比特控制电路控制,量子比特读出电路在量子比特控制电路的控制下测量量子比特器件的量子态,并根据测量结果提供量子比特读出。</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=88ad0e44-80d4-439c-b505-c7a5d8291a92&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=G9LfKTB8JnqoRI2Dn8R4dRfNs%2F2jOb1qytdxeOVTk6c%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>超导量子处理电路中的可调谐量子比特器件</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RIGETTI &amp; CO INC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SETE, EYOB A. | CHEN, ANGELA Q. | POLETTO, STEFANO | KULSHRESHTHA, SHOBHAN | MANENTI, RICCARDO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>一般而言,超导量子处理电路包含一个可调谐量子比特器件。该可调谐量子比特器件包含一个电路环路,该电路环路配置成在可调谐量子比特器件工作期间接收磁通量,该磁通量控制该可调谐量子比特器件的量子比特频率。在一些实施例中,该电路环路由以下部分组成:一个非线性电路元件和一个或多个线性电路元件。该单个非线性电路元件是连接在第一电路节点和第二电路节点之间的约瑟夫森结。该一个或多个线性电路元件包括一个与连接在第一电路节点和第二电路节点之间的约瑟夫森结并联的线性电感器。</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=7ee4ebb7-bf1f-4709-9bd8-e2c11c904371&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=113QyBsuqSB7ew5nF5t9X7v8ckZq86qN%2FYBOiHEoKcY%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>带有嵌入式读出的紧凑型硅量子比特单元</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>量子运动科技有限公司</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GONZALEZ-ZALBA, MIGUEL FERNANDO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>本发明公开了一种量子器件,该器件具有用于执行量子比特测量或读出的LC谐振器电路。该器件包括硅层( 601 ),介电层( 603 ) 布置在硅层上并与硅层形成功能界面( 601 ),第一金属区( 614 )布置在介电层上603以及第二个金属区域( 624 )布置在介电层上603并与第一金属区域横向分离( 614第一和第二金属区( 614, 624 )被布置成电连接,使得可以在第一和第二金属区域下方感应出一个双量子点,形成一个具有第一态和第二态的量子比特( 614, 624在功能界面处。双量子点提供了一个电容 C 1在LC谐振器电路中,双量子点的电容取决于量子比特的状态。第一个金属区域( 614 ) 提供一个电感器 L 1在 LC 谐振器电路中,LC 谐振器电路的谐振频率取决于量子比特的状态,因此可以测量或推断量子比特的状态。</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=c4572404-b8ad-47b4-9a02-11d0d900b01a&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=hfKywHVMw%2BVdoUO9gdOfjExUoagn07uL2GPrjy0yOIY%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>用于量子计算误差抑制的分层噪声自适应控制系统及方法</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IEN ARCHITECT OFFICE CO LTD</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>정찬희</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>本发明涉及一种用于减少量子计算环境中物理误差的分层控制系统和方法。本发明利用包含室温控制代理(RTAA)和近端硬件控制器(NHC)的双层控制结构,实现了实时脉冲控制和自适应噪声参数更新的并行执行。 
-具体而言,本发明包括:(1) 噪声不对称反向镜像 (NAEM),用于反转超导量子比特 T1 弛豫方向的不对称性;(2) 节律频谱指纹识别 (RSF),通过对门脉冲施加周期性调制,为解码器输入提供结构特征量;(3) 经典顺序引导序列化 (CGS),用作辅助元数据通道,用于检测经典控制通道的顺序计数器异常;以及 (4) 分层自适应控制 (HAC),用于分离室温控制代理和近端硬件控制器的角色。 
-本发明涉及一种在保持现有电路功能结构的同时自适应地优化执行控制参数的技术,而对电路结构本身的改变,例如逻辑量子比特和物理量子比特之间的重新映射、重新排列门执行顺序或重新配置电路深度,并非本发明的直接主题。</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=4e488ee2-feac-4374-af22-02ceaaf24a98&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=n1OpBWABvcgiGtIaeCREOf1jZGqGWQc8e7CdYxtG6Mg%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=1f47e0c7-88cb-480e-a7ae-4febb8a3e7ff&amp;shareId=4G0297G6-613E-5D50-0F19-1180B5GF30B6&amp;from=EXPORT&amp;signature=8EIoDq3OQi8gSMy%2FjYxsGCrcMLVQY7Uzb9K8gG6gugU%3D&amp;expire=94608000&amp;date=20260626T004457Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_超导量子测控技术.xlsx
+++ b/weekly_temp/patents_超导量子测控技术.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>用于量子数据查找的电路设计</t>
+          <t>超导量子位中的光控制的二能级系统的量子位选择性调谐</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>微软技术许可有限责任公司</t>
+          <t>国际商业机器公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SUNDARAM, AARTHI MEENAKSHI | ZHU, SHUCHEN | LOW, GUANG HAO</t>
+          <t>SANDBERG, MARTIN O. | FALK, ABRAM L. | BALAKRISHNAN, KARTHIK | ORCUTT, JASON S.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,54 +476,204 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本公开的方面包括一种量子查找技术。这些方面包括:响应于接收输入,将输入路由通过第一量子路由器以确定第一输出。这些方面包括:将第一输出路由到至少一个第二量子路由器,该至少一个第二量子路由器将第一输出馈送到门树,该门树生成第二输出,该第二输出被馈送到量子位,量子位执行操作并生成读出。这些方面包括:将读出路由通过第三量子路由器,该第三量子路由器被布置用于输出读出。</t>
+          <t>提供了用于减轻量子处理器中的缺陷的影响的方法和系统。减轻系统包括具有多个量子位的量子处理器。该系统包括发光源阵列。每个发光源与量子处理器上的量子位对准。该系统包括控制器,该控制器被配置为接收对量子位的选择并且使得来自发光源阵列的发光源向所选择的量子位发射光。光用于混乱量子处理器中的强耦合的两能级系统(TLS)。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=b499c2e1-f153-4f19-a7e8-6ee31a3a32cf&amp;shareId=4G0297G6-613E-5D50-0F19-1180B5GF30B6&amp;from=EXPORT&amp;signature=FjmTR%2Ftxl92ABHSVId64caGwZfwno5i3ahDj%2FpWgmLQ%3D&amp;expire=94608000&amp;date=20260626T004457Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=64917608-271c-47fc-88fd-50abd7014bb1&amp;shareId=G8BF057F-0661-7116-129B-3907C36294E3&amp;from=EXPORT&amp;signature=xR2N5PteLx4IdUbLS3i0AfodieQal1r5j5XMH%2FFSlw0%3D&amp;expire=94608000&amp;date=20260710T002653Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>使用超导刚挠电路支持量子位平面与量子位平面的控制系统之间的高热梯度的系统和方法</t>
+          <t>参数激活的量子逻辑门</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>微软技术许可有限责任公司</t>
+          <t>RIGETTI &amp; CO INC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TURNER, MATTHEW DAVID | RANTA, CRAIG STEVEN | KRAMER, KEVIN JAMES</t>
+          <t>SETE, EYOB A. | DIDIER, NICOLAS | DA SILVA, MARCUS PALMER | RIGETTI, CHAD TYLER | REAGOR, MATTHEW J. | CALDWELL, SHANE ARTHUR | TEZAK, NIKOLAS ANTON | RYAN, COLM ANDREW | HONG, SABRINA SAE BYUL | SIVARAJAH, PRASAHNT | PAPAGEORGE, ALEXANDER | ABRAMS, DEANNA MARGO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>一般来说,量子逻辑门是在量子计算系统中实现的。在某些情况下,量子处理器中定义了一对量子比特;这对量子比特可以包括由量子处理器中的第一量子比特器件定义的第一量子比特,以及由量子处理器中可调谐量子比特器件定义的第二量子比特。通过向与可调谐量子比特器件耦合的控制线发送控制信号,可以对这对量子比特应用量子逻辑门。控制信号可以配置为以调制频率调制可调谐量子比特器件的跃迁频率,而调制频率可以根据第一量子比特器件的跃迁频率确定。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=2d10d7dd-6de4-4689-b074-a8c714ebc258&amp;shareId=G8BF057F-0661-7116-129B-3907C36294E3&amp;from=EXPORT&amp;signature=elMhQaQLC43N%2BQ9JLCL9z4H0p6gIZdulULzSsB67rzk%3D&amp;expire=94608000&amp;date=20260710T002653Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>量子器件、量子计算系统以及读取量子器件的方法</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>富士通株式会社 | 独立行政法人理化学研究所</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>才田 大輔 | 玉手 修平</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>公开专利</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>本文描述了用于在量子比特平面和该量子比特平面的控制系统之间维持高温度梯度的系统和方法。该系统包括与超导刚挠性电路的第一刚性电路部分关联的量子比特平面,以及与该超导刚挠性电路的第二刚性电路部分关联的控制系统。该超导刚挠性电路包括用于连接第一刚性电路部分和第二刚性电路部分的柔性电路部分。该系统还包括第一冷却系统,用于将量子比特平面和超导刚挠性电路的第一刚性电路部分的工作温度维持在100毫开尔文或以下。该系统还包括第二冷却系统,用于将控制系统和超导刚挠性电路的第二刚性电路部分的工作温度维持在10开尔文或以下。</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=1f47e0c7-88cb-480e-a7ae-4febb8a3e7ff&amp;shareId=4G0297G6-613E-5D50-0F19-1180B5GF30B6&amp;from=EXPORT&amp;signature=8EIoDq3OQi8gSMy%2FjYxsGCrcMLVQY7Uzb9K8gG6gugU%3D&amp;expire=94608000&amp;date=20260626T004457Z&amp;version=1.0</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>本发明提供了一种量子器件、一种量子计算系统以及一种读取量子器件的方法,该方法可以对多个量子比特电路执行多次读取。 
+ 【解决方案】该量子器件包括第一量子比特电路、第二量子比特电路和盖芯片,其中,第一量子比特电路包括第一端口、第一量子比特以及耦合至第一量子比特和第一端口并具有第一谐振频率的第一谐振器;第二量子比特电路包括第二端口、第二量子比特以及耦合至第二量子比特和第二端口并具有不同于第一谐振频率的第二谐振频率的第二谐振器;盖芯片包括耦合至第一端口和第二端口的波导。该量子器件可用于例如量子计算。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=ad4b5a44-eb9e-43b0-a627-c4e61649e9f2&amp;shareId=G8BF057F-0661-7116-129B-3907C36294E3&amp;from=EXPORT&amp;signature=T3SM1XZ3PSuT8z1i5wc2VWfAEterg2zsFUlXWwLshSU%3D&amp;expire=94608000&amp;date=20260710T002653Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>信息处理方法、信息处理系统、计算量子电路、生成计算量子电路的方法和程序</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>株式会社QUEMIX | 国立大学法人东京科学大学</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>西 紘史 | 小杉 太一 | 松下 雄一郎</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>提供一种量子算法,可以方便高效地获得所需的量子态。 
+ 【解决方案】该方法包括以下步骤:获取由n个计算量子比特表示的输入状态信息、哈密顿量信息以及基于该哈密顿量的操作的迭代次数K(K为大于等于2的整数);根据K分配多个辅助比特;以及基于所获取的结果生成对计算量子比特和辅助比特进行操作的计算量子电路。该计算量子电路配置为对n个计算量子比特进行操作,并包括与每个分配的辅助比特对应的单元门操作,每个单元门操作以多个不同的辅助比特之一作为控制比特,以计算量子比特作为目标比特,根据辅助比特的状态改变对计算量子比特的操作模式,并基于辅助比特的观测结果输出计算量子比特的状态作为计算结果。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=ba99e784-a5c2-461c-bdbd-495437ba9281&amp;shareId=G8BF057F-0661-7116-129B-3907C36294E3&amp;from=EXPORT&amp;signature=kMgYDt%2FRfpeGiyrARyHnBp7xSNMLER5a2JYkG0KR218%3D&amp;expire=94608000&amp;date=20260710T002653Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>闭环量子比特校准技术</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>英特尔公司</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>수브라마니안, 수실 | 레빙거, 런 | 슈마커, 에브게니</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>本文公开了一种用于控制自旋量子比特的脉冲闭环校准技术。在一个示例性实施例中,校准电路利用脉冲发生器产生脉冲。这些脉冲通过一个由滤波器参数控制的可变滤波器。脉冲被施加到量子比特上,并对其进行测量。根据测量得到的量子比特状态,可以改变滤波器参数。这样,​​就可以快速连续地校准控制脉冲。该校准方法具有多项优势。它可以由靠近物理量子比特的电路实现,从而降低噪声、串扰等干扰的可能性。该校准方法具有可扩展性,因为可以对给定的量子比特快速连续地进行校准,并且同一个校准电路可以复用以与多个量子比特连接。校准电路可以位于集成电路上,该集成电路可以位于量子计算机的低温级内。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=33a6ba33-ee84-4c24-ad07-0c2ca5864d0c&amp;shareId=G8BF057F-0661-7116-129B-3907C36294E3&amp;from=EXPORT&amp;signature=KHQUzOyGS6LMeS5eoxCgbQ1G9lRb9BWZr9sGKWPvB9Q%3D&amp;expire=94608000&amp;date=20260710T002653Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>用于优化自旋量子比特读取的系统和方法</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>硅量子计算私人有限公司</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>고먼, 새뮤얼 키스 | 겅, 헬렌 | 키친스키, 미첼 | 오시카, 에디타 | 시먼스, 미셸 이본</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>本公开的各个方面提供了利用已知读出技术优化量子比特读出的机制。为此,本公开的某些方面控制了被测量子比特与电荷传感器/存储器之间的隧穿速率。如果量子处理系统优选基于PSB的读出,则本公开的各个方面会增加与SET/存储器隧穿耦合的两个量子点之间的隧穿速率不对称性。如果量子处理系统优选基于存储器的读出,则本公开的各个方面会调整量子点与SET/存储器之间的隧穿速率,以提高读出方法的效率。</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=6abbfff6-6d37-4f61-a3c4-60bd2d8f7c5d&amp;shareId=G8BF057F-0661-7116-129B-3907C36294E3&amp;from=EXPORT&amp;signature=h8oQ0dHWLBpCgKqmMeCkGAQfBibFPJHQ4yX%2BW2%2FwqzE%3D&amp;expire=94608000&amp;date=20260710T002653Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_超导量子测控技术.xlsx
+++ b/weekly_temp/patents_超导量子测控技术.xlsx
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>超导量子位中的光控制的二能级系统的量子位选择性调谐</t>
+          <t>一种超导量子比特量子态读取方法、装置、设备及介质</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>国际商业机器公司</t>
+          <t>量子科技长三角产业创新中心</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SANDBERG, MARTIN O. | FALK, ABRAM L. | BALAKRISHNAN, KARTHIK | ORCUTT, JASON S.</t>
+          <t>周慧德 | 李泽东 | 王天骐 | 栾添 | 潘文杰</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,34 +476,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>提供了用于减轻量子处理器中的缺陷的影响的方法和系统。减轻系统包括具有多个量子位的量子处理器。该系统包括发光源阵列。每个发光源与量子处理器上的量子位对准。该系统包括控制器,该控制器被配置为接收对量子位的选择并且使得来自发光源阵列的发光源向所选择的量子位发射光。光用于混乱量子处理器中的强耦合的两能级系统(TLS)。</t>
+          <t>本发明涉及量子比特读取领域，特别是涉及一种超导量子比特量子态读取方法、装置、设备及介质，通过向超导量子芯片发送读取驱动信号；所述读取驱动信号为包括超导量子比特的|0&amp;gt;态谐振频率及|1&amp;gt;态谐振频率的变频信号；从所述超导量子芯片采集读取反馈信号；根据所述读取反馈信号、预存储的对应所述读取驱动信号的|0&amp;gt;态响应信号及|1&amp;gt;态响应信号，通过相关性分析确定所述超导量子比特的量子态。本发明使用变频信号作为所述读取驱动信号，能减低系统对于频率无关噪声的敏感，提升信号的信噪比，还有，相关性计算不需要再转换到IQ平面，减少了计算的步骤，且相关分析的算法通常可以使用硬件加速，降低了解算的资源消耗，提升了运算效率。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=64917608-271c-47fc-88fd-50abd7014bb1&amp;shareId=G8BF057F-0661-7116-129B-3907C36294E3&amp;from=EXPORT&amp;signature=xR2N5PteLx4IdUbLS3i0AfodieQal1r5j5XMH%2FFSlw0%3D&amp;expire=94608000&amp;date=20260710T002653Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=06b69bba-8a14-46cc-b46d-69ba25bcb8cb&amp;shareId=4B84F79D-414E-727D-271B-84EBE715CCCG&amp;from=EXPORT&amp;signature=5Y0jRBK9UmAkVvD5dA6xkkIKh1sqaj6KMTBClfPTU3E%3D&amp;expire=94608000&amp;date=20260717T010927Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>参数激活的量子逻辑门</t>
+          <t>量子信号处理方法、装置、设备及存储介质</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RIGETTI &amp; CO INC</t>
+          <t>北京百度网讯科技有限公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SETE, EYOB A. | DIDIER, NICOLAS | DA SILVA, MARCUS PALMER | RIGETTI, CHAD TYLER | REAGOR, MATTHEW J. | CALDWELL, SHANE ARTHUR | TEZAK, NIKOLAS ANTON | RYAN, COLM ANDREW | HONG, SABRINA SAE BYUL | SIVARAJAH, PRASAHNT | PAPAGEORGE, ALEXANDER | ABRAMS, DEANNA MARGO</t>
+          <t>郭学仪 | 王贺</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,110 +513,108 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>一般来说,量子逻辑门是在量子计算系统中实现的。在某些情况下,量子处理器中定义了一对量子比特;这对量子比特可以包括由量子处理器中的第一量子比特器件定义的第一量子比特,以及由量子处理器中可调谐量子比特器件定义的第二量子比特。通过向与可调谐量子比特器件耦合的控制线发送控制信号,可以对这对量子比特应用量子逻辑门。控制信号可以配置为以调制频率调制可调谐量子比特器件的跃迁频率,而调制频率可以根据第一量子比特器件的跃迁频率确定。</t>
+          <t>本公开提供了量子信号处理方法、装置、设备及存储介质，涉及数据处理领域，尤其涉及量子计算、超导量子计算、量子控制等技术领域。具体实现方案为：基于多个激发频率中各激发频率所对应的目标幅度和目标相位，以及多个参考频率中各参考频率所对应的目标幅度和目标相位，得到各参考频率所对应的初始谱线；其中，激发频率表示用于激发量子比特的微波脉冲的频率；参考频率所对应的初始谱线用于表示在参考频率的基础上、量子比特的激发状态信息随激发频率的变化程度；确定各参考频率所对应的初始谱线的信噪比；基于各参考频率所对应的初始谱线的信噪比，得到信噪比满足预设要求的目标谱线。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=2d10d7dd-6de4-4689-b074-a8c714ebc258&amp;shareId=G8BF057F-0661-7116-129B-3907C36294E3&amp;from=EXPORT&amp;signature=elMhQaQLC43N%2BQ9JLCL9z4H0p6gIZdulULzSsB67rzk%3D&amp;expire=94608000&amp;date=20260710T002653Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=af5f5006-73a0-4799-b40d-79cc68b56beb&amp;shareId=4B84F79D-414E-727D-271B-84EBE715CCCG&amp;from=EXPORT&amp;signature=%2BDaBnwCg5e5j2q8ac8OIU8ROgmQcs5HJucsT8KJkLIw%3D&amp;expire=94608000&amp;date=20260717T010927Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>量子器件、量子计算系统以及读取量子器件的方法</t>
+          <t>量子测控参数的处理方法、装置、设备及存储介质</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>富士通株式会社 | 独立行政法人理化学研究所</t>
+          <t>北京百度网讯科技有限公司</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>才田 大輔 | 玉手 修平</t>
+          <t>孟则霖</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>本发明提供了一种量子器件、一种量子计算系统以及一种读取量子器件的方法,该方法可以对多个量子比特电路执行多次读取。 
- 【解决方案】该量子器件包括第一量子比特电路、第二量子比特电路和盖芯片,其中,第一量子比特电路包括第一端口、第一量子比特以及耦合至第一量子比特和第一端口并具有第一谐振频率的第一谐振器;第二量子比特电路包括第二端口、第二量子比特以及耦合至第二量子比特和第二端口并具有不同于第一谐振频率的第二谐振频率的第二谐振器;盖芯片包括耦合至第一端口和第二端口的波导。该量子器件可用于例如量子计算。</t>
+          <t>本公开提供了量子测控参数的处理方法、装置、设备及其存储介质，涉及数据处理领域，尤其涉及量子计算、超导量子计算、量子控制等技术领域。具体实现方案为：确定第一初始映射关系B2F，其中，所述第一初始映射关系B2F是对目标集合所包含的二元采样组进行拟合处理所得，能够表征量子比特的偏置值至量子比特的比特频率的映射关系；在确定第一初始映射关系B2F中包含有预设偏置值下的情况下，以及用于拟合的目标集合达到采样终止条件的情况下，基于目标集合所包含的各二元采样组，拟合得到目标映射关系B2F*；其中，目标映射关系B2F*用于表征量子比特的偏置值与量子比特的比特频率之间的映射关系。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=ad4b5a44-eb9e-43b0-a627-c4e61649e9f2&amp;shareId=G8BF057F-0661-7116-129B-3907C36294E3&amp;from=EXPORT&amp;signature=T3SM1XZ3PSuT8z1i5wc2VWfAEterg2zsFUlXWwLshSU%3D&amp;expire=94608000&amp;date=20260710T002653Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=32218791-5383-4352-a016-7cff3fb3988b&amp;shareId=4B84F79D-414E-727D-271B-84EBE715CCCG&amp;from=EXPORT&amp;signature=PBjJlCdDrkhX6bJ4yuaPQqMhknTWMFHVGJuZIwcFkQ0%3D&amp;expire=94608000&amp;date=20260717T010927Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>信息处理方法、信息处理系统、计算量子电路、生成计算量子电路的方法和程序</t>
+          <t>测控系统、测控方法及量子计算设备</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>株式会社QUEMIX | 国立大学法人东京科学大学</t>
+          <t>成都中微达信科技有限公司</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>西 紘史 | 小杉 太一 | 松下 雄一郎</t>
+          <t>林海川 | 王亚男 | 王渊 | 许凡 | 邹小波 | 吴峰</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>提供一种量子算法,可以方便高效地获得所需的量子态。 
- 【解决方案】该方法包括以下步骤:获取由n个计算量子比特表示的输入状态信息、哈密顿量信息以及基于该哈密顿量的操作的迭代次数K(K为大于等于2的整数);根据K分配多个辅助比特;以及基于所获取的结果生成对计算量子比特和辅助比特进行操作的计算量子电路。该计算量子电路配置为对n个计算量子比特进行操作,并包括与每个分配的辅助比特对应的单元门操作,每个单元门操作以多个不同的辅助比特之一作为控制比特,以计算量子比特作为目标比特,根据辅助比特的状态改变对计算量子比特的操作模式,并基于辅助比特的观测结果输出计算量子比特的状态作为计算结果。</t>
+          <t>本申请提供一种测控系统、测控方法及量子计算设备，涉及量子计算技术领域。测控系统包括：量子芯片、功能单元、交换单元和上位机；上位机用于控制功能单元进行工作，功能单元用于测控量子芯片的量子计算；功能单元包括具有统一接口的低噪声电压单元、任意波形发生单元、射频任意波发生单元、反射测量单元、微波激励单元、同步扩展单元和快速反馈单元。测控方法包括：通过上位机，控制功能单元中的同步扩展单元输出时钟信号；通过上位机，控制功能单元进入时钟同步模式；通过上位机，控制同步扩展单元输出同步触发信号；通过功能单元，基于接收的同步触发信号同步内部的时钟接口，输出同步时钟信号；通过上位机，控制功能单元进入工作模式。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=ba99e784-a5c2-461c-bdbd-495437ba9281&amp;shareId=G8BF057F-0661-7116-129B-3907C36294E3&amp;from=EXPORT&amp;signature=kMgYDt%2FRfpeGiyrARyHnBp7xSNMLER5a2JYkG0KR218%3D&amp;expire=94608000&amp;date=20260710T002653Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=6f0d91b0-2bc7-4be8-9cbe-53756b0b5d06&amp;shareId=4B84F79D-414E-727D-271B-84EBE715CCCG&amp;from=EXPORT&amp;signature=fkA6W8Am4ORdYefvnBfZAxUNTeqGik%2FKdM9TM02AL%2BI%3D&amp;expire=94608000&amp;date=20260717T010927Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>闭环量子比特校准技术</t>
+          <t>一种读取频率标定方法、装置、设备及可读存储介质</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>英特尔公司</t>
+          <t>山东云海国创云计算装备产业创新中心有限公司</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>수브라마니안, 수실 | 레빙거, 런 | 슈마커, 에브게니</t>
+          <t>李尚书 | 刘强</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -626,34 +624,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>本文公开了一种用于控制自旋量子比特的脉冲闭环校准技术。在一个示例性实施例中,校准电路利用脉冲发生器产生脉冲。这些脉冲通过一个由滤波器参数控制的可变滤波器。脉冲被施加到量子比特上,并对其进行测量。根据测量得到的量子比特状态,可以改变滤波器参数。这样,​​就可以快速连续地校准控制脉冲。该校准方法具有多项优势。它可以由靠近物理量子比特的电路实现,从而降低噪声、串扰等干扰的可能性。该校准方法具有可扩展性,因为可以对给定的量子比特快速连续地进行校准,并且同一个校准电路可以复用以与多个量子比特连接。校准电路可以位于集成电路上,该集成电路可以位于量子计算机的低温级内。</t>
+          <t>本发明公开了一种读取频率标定方法、装置、设备及可读存储介质，应用于量子领域，包括：对读取线上的读取腔进行频率扫描，得到扫描数据；基于扫描数据进行自适应寻峰处理，并通过参数调节使寻峰得到的频率数量与读取腔的数量一致，生成读取频率候选列表；读取频率候选列表中包含各峰值对应的实际读取频率；基于读取频率候选列表为各量子比特分配待验证读取频率，通过改变量子比特的信号偏置进行频率扫描，确定每个量子比特绑定的读取腔，以及最终对应的读取频率。本发明可以自动化标定一条读取线上所有读取腔的读取频率并确认其与量子比特的连接关系，保障后续量子比特状态读取的准确性，以及减少人力与时间的资源消耗。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=33a6ba33-ee84-4c24-ad07-0c2ca5864d0c&amp;shareId=G8BF057F-0661-7116-129B-3907C36294E3&amp;from=EXPORT&amp;signature=KHQUzOyGS6LMeS5eoxCgbQ1G9lRb9BWZr9sGKWPvB9Q%3D&amp;expire=94608000&amp;date=20260710T002653Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=606618bf-4f37-44d1-babb-5c7285a48bed&amp;shareId=4B84F79D-414E-727D-271B-84EBE715CCCG&amp;from=EXPORT&amp;signature=arZXB8CEMg6SAGFUbnrUeOsOJMNFDKw%2FOkBX%2FTXfk14%3D&amp;expire=94608000&amp;date=20260717T010927Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>用于优化自旋量子比特读取的系统和方法</t>
+          <t>一种用于量子芯片的参数校准方法及系统</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>硅量子计算私人有限公司</t>
+          <t>量子科技长三角产业创新中心 | 中电科国基量子产业(苏州)有限公司</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>고먼, 새뮤얼 키스 | 겅, 헬렌 | 키친스키, 미첼 | 오시카, 에디타 | 시먼스, 미셸 이본</t>
+          <t>陈玉光 | 王碧莹</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -663,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>本公开的各个方面提供了利用已知读出技术优化量子比特读出的机制。为此,本公开的某些方面控制了被测量子比特与电荷传感器/存储器之间的隧穿速率。如果量子处理系统优选基于PSB的读出,则本公开的各个方面会增加与SET/存储器隧穿耦合的两个量子点之间的隧穿速率不对称性。如果量子处理系统优选基于存储器的读出,则本公开的各个方面会调整量子点与SET/存储器之间的隧穿速率,以提高读出方法的效率。</t>
+          <t>本公开提供了一种用于量子芯片的参数校准方法及系统，方法包括获取校准的原始数据；对原始数据进行第一层级评估，若数据质量不满足标准则执行第一重试策略，调整硬件参数重新获取数据；若满足标准则对中间分析结果进行第二层级评估，若结果不满足标准则判定失效类型；若为实验参数失配则执行第一重试策略，若为算法失配则执行第二重试策略调整算法；当双重评估均通过时输出最终校准参数，校准方法将输出参数应用于量子芯片。本公开通过双重评估与两级重试，提升校准成功率与准确性。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=6abbfff6-6d37-4f61-a3c4-60bd2d8f7c5d&amp;shareId=G8BF057F-0661-7116-129B-3907C36294E3&amp;from=EXPORT&amp;signature=h8oQ0dHWLBpCgKqmMeCkGAQfBibFPJHQ4yX%2BW2%2FwqzE%3D&amp;expire=94608000&amp;date=20260710T002653Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=5b6aca0e-9969-4dc7-b092-f307debaa46f&amp;shareId=4B84F79D-414E-727D-271B-84EBE715CCCG&amp;from=EXPORT&amp;signature=Ea9Lvu%2FeM1ETiEb99IcYydgn%2BOXuVZw7MzJIfsP6N58%3D&amp;expire=94608000&amp;date=20260717T010927Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_超导量子测控技术.xlsx
+++ b/weekly_temp/patents_超导量子测控技术.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>一种超导量子比特量子态读取方法、装置、设备及介质</t>
+          <t>量子处理系统</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>量子科技长三角产业创新中心</t>
+          <t>硅量子计算私人有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>周慧德 | 李泽东 | 王天骐 | 栾添 | 潘文杰</t>
+          <t>SIMMONS, MICHELLE YVONNE | HOUSE, MATTHEW GREGORY | GORMAN, SAMUEL KEITH | HOGG, MARK RICHARD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,34 +476,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本发明涉及量子比特读取领域，特别是涉及一种超导量子比特量子态读取方法、装置、设备及介质，通过向超导量子芯片发送读取驱动信号；所述读取驱动信号为包括超导量子比特的|0&amp;gt;态谐振频率及|1&amp;gt;态谐振频率的变频信号；从所述超导量子芯片采集读取反馈信号；根据所述读取反馈信号、预存储的对应所述读取驱动信号的|0&amp;gt;态响应信号及|1&amp;gt;态响应信号，通过相关性分析确定所述超导量子比特的量子态。本发明使用变频信号作为所述读取驱动信号，能减低系统对于频率无关噪声的敏感，提升信号的信噪比，还有，相关性计算不需要再转换到IQ平面，减少了计算的步骤，且相关分析的算法通常可以使用硬件加速，降低了解算的资源消耗，提升了运算效率。</t>
+          <t>本公开涉及量子处理系统,该系统包括位于半导体衬底上的多个供体原子量子比特。该系统还包括多个用于控制供体原子量子比特的控制门。该系统还包括制造在半导体衬底上/内部的超晶格量子点(SLQD)电荷传感器。该SLQD电荷传感器用于检测位于其检测范围内的两个或多个供体原子量子比特的自旋态。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=06b69bba-8a14-46cc-b46d-69ba25bcb8cb&amp;shareId=4B84F79D-414E-727D-271B-84EBE715CCCG&amp;from=EXPORT&amp;signature=5Y0jRBK9UmAkVvD5dA6xkkIKh1sqaj6KMTBClfPTU3E%3D&amp;expire=94608000&amp;date=20260717T010927Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=de02e88f-ab34-41f9-bdca-1d6f631500dc&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=8uajQVCH%2BY1pHEWnSER4rQjXx9lvEeJ%2BHGdWgSQE5ls%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>量子信号处理方法、装置、设备及存储介质</t>
+          <t>量子比特的加性控制实现了时域和频域复用。</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>北京百度网讯科技有限公司</t>
+          <t>IQM芬兰有限公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>郭学仪 | 王贺</t>
+          <t>ヘインスー ヨハネス</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,34 +513,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本公开提供了量子信号处理方法、装置、设备及存储介质，涉及数据处理领域，尤其涉及量子计算、超导量子计算、量子控制等技术领域。具体实现方案为：基于多个激发频率中各激发频率所对应的目标幅度和目标相位，以及多个参考频率中各参考频率所对应的目标幅度和目标相位，得到各参考频率所对应的初始谱线；其中，激发频率表示用于激发量子比特的微波脉冲的频率；参考频率所对应的初始谱线用于表示在参考频率的基础上、量子比特的激发状态信息随激发频率的变化程度；确定各参考频率所对应的初始谱线的信噪比；基于各参考频率所对应的初始谱线的信噪比，得到信噪比满足预设要求的目标谱线。</t>
+          <t>该量子电子电路包括量子电路元件 (101)、控制信号线 (102, 103) 以及位于控制信号线 (102, 103) 和量子电路元件 (101) 之间的信号耦合单元,用于将至少部分控制信号线 (102, 103) 耦合到至少部分量子电路元件 (101)。控制信号线至少分为第一子集 (102) 和第二子集 (103)。信号耦合单元将至少一个子组中的每个量子电路元件 (101) 分别耦合到第一子集 (102) 和第二子集 (103) 的相应控制信号线。这样,子组中各个量子电路元件 (101) 的状态就可以通过分别经由第一子集 (102) 和第二子集 (103) 的相应控制信号线传输的加性控制信号进行加性控制。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=af5f5006-73a0-4799-b40d-79cc68b56beb&amp;shareId=4B84F79D-414E-727D-271B-84EBE715CCCG&amp;from=EXPORT&amp;signature=%2BDaBnwCg5e5j2q8ac8OIU8ROgmQcs5HJucsT8KJkLIw%3D&amp;expire=94608000&amp;date=20260717T010927Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=8bb19c6f-53e7-456b-abb8-fe646424e372&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=9ZlsJJzic0eXWeJSC7DzdTnAExam%2BdZ7MQetjlKJeVc%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>量子测控参数的处理方法、装置、设备及存储介质</t>
+          <t>波形处理方法、测控系统、量子计算机、介质和设备</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>北京百度网讯科技有限公司</t>
+          <t>本源量子计算科技(合肥)股份有限公司</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>孟则霖</t>
+          <t>请求不公布姓名 | 孔伟成</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -550,34 +550,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>本公开提供了量子测控参数的处理方法、装置、设备及其存储介质，涉及数据处理领域，尤其涉及量子计算、超导量子计算、量子控制等技术领域。具体实现方案为：确定第一初始映射关系B2F，其中，所述第一初始映射关系B2F是对目标集合所包含的二元采样组进行拟合处理所得，能够表征量子比特的偏置值至量子比特的比特频率的映射关系；在确定第一初始映射关系B2F中包含有预设偏置值下的情况下，以及用于拟合的目标集合达到采样终止条件的情况下，基于目标集合所包含的各二元采样组，拟合得到目标映射关系B2F*；其中，目标映射关系B2F*用于表征量子比特的偏置值与量子比特的比特频率之间的映射关系。</t>
+          <t>本申请提供了波形处理方法、测控系统、量子计算机、介质和设备，所述方法包括：接收传输波形指令和扫描数据；使用所述扫描数据处理所述传输波形指令，以得到多个输出波形指令；将所述输出波形指令编译成实际波形数据，所述实际波形数据用于在量子计算测控实验任务中对量子比特进行控制或者测量。本申请允许对扫描数据与传输波形指令进行分离传输处理，实现内存的压缩，在编译过程中，所占用的内存较少，能够显著改善内存不足问题，降低任务失败风险，促进量子计算测控实验任务顺利完成，简化波形拼接等操作，允许用户更自由、灵活地去定义实验过程，不仅压缩量子计算测控实验的传输数据量，还有利于解耦实验和硬件，实现跨平台的兼容性。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=32218791-5383-4352-a016-7cff3fb3988b&amp;shareId=4B84F79D-414E-727D-271B-84EBE715CCCG&amp;from=EXPORT&amp;signature=PBjJlCdDrkhX6bJ4yuaPQqMhknTWMFHVGJuZIwcFkQ0%3D&amp;expire=94608000&amp;date=20260717T010927Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=04421a75-2c47-4bb8-ab9e-d0027df4377f&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=586qTljgnHyuxvIWxVfqucItJIHechPYEqTjnLxKvMI%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>测控系统、测控方法及量子计算设备</t>
+          <t>针对延展十字码的稳定子测量方法、装置、设备及存储介质</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>成都中微达信科技有限公司</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>林海川 | 王亚男 | 王渊 | 许凡 | 邹小波 | 吴峰</t>
+          <t>陈建鑫 | 周润石</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -587,34 +587,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>本申请提供一种测控系统、测控方法及量子计算设备，涉及量子计算技术领域。测控系统包括：量子芯片、功能单元、交换单元和上位机；上位机用于控制功能单元进行工作，功能单元用于测控量子芯片的量子计算；功能单元包括具有统一接口的低噪声电压单元、任意波形发生单元、射频任意波发生单元、反射测量单元、微波激励单元、同步扩展单元和快速反馈单元。测控方法包括：通过上位机，控制功能单元中的同步扩展单元输出时钟信号；通过上位机，控制功能单元进入时钟同步模式；通过上位机，控制同步扩展单元输出同步触发信号；通过功能单元，基于接收的同步触发信号同步内部的时钟接口，输出同步时钟信号；通过上位机，控制功能单元进入工作模式。</t>
+          <t>本申请提供一种针对延展十字码的稳定子测量方法、装置、设备及存储介质，在症状提取周期的第一处理阶段，将X辅助量子比特与数据量子比特Ak+1执行CNOT门；从数据量子比特Ak到数据量子比特Am+1，依次与X辅助量子比特执行目标双比特门；将Z辅助量子比特与数据量子比特执行CNOT门；从数据量子比特到数据量子比特Am，依次与Z辅助量子比特执行目标双比特门；在第二处理阶段，将目标辅助量子比特与数据量子比特执行CNOT门；控制数据量子比特至数据量子比特Bk，依次与目标辅助量子比特执行目标双比特门；将目标辅助量子比特与数据量子比特Bk+1执行CNOT门；在第三处理阶段后，确定延展十字码中X稳定子和Z稳定子的测量数据。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=6f0d91b0-2bc7-4be8-9cbe-53756b0b5d06&amp;shareId=4B84F79D-414E-727D-271B-84EBE715CCCG&amp;from=EXPORT&amp;signature=fkA6W8Am4ORdYefvnBfZAxUNTeqGik%2FKdM9TM02AL%2BI%3D&amp;expire=94608000&amp;date=20260717T010927Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=a6acd9eb-0c6f-440e-bf4f-ff1268703a36&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=oGaZ0B49phirzh6bOJFN43KfkVkzyQh7YVhU5Qf9g2Q%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>一种读取频率标定方法、装置、设备及可读存储介质</t>
+          <t>量子比特控制程序、量子比特控制方法和信息处理装置。</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>山东云海国创云计算装备产业创新中心有限公司</t>
+          <t>富士通株式会社</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>李尚书 | 刘强</t>
+          <t>阿部 徹 | 杉山 太香典</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,34 +624,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>本发明公开了一种读取频率标定方法、装置、设备及可读存储介质，应用于量子领域，包括：对读取线上的读取腔进行频率扫描，得到扫描数据；基于扫描数据进行自适应寻峰处理，并通过参数调节使寻峰得到的频率数量与读取腔的数量一致，生成读取频率候选列表；读取频率候选列表中包含各峰值对应的实际读取频率；基于读取频率候选列表为各量子比特分配待验证读取频率，通过改变量子比特的信号偏置进行频率扫描，确定每个量子比特绑定的读取腔，以及最终对应的读取频率。本发明可以自动化标定一条读取线上所有读取腔的读取频率并确认其与量子比特的连接关系，保障后续量子比特状态读取的准确性，以及减少人力与时间的资源消耗。</t>
+          <t>减小用于控制量子比特的脉冲信号的参数。 
+ 【解决方案】信息处理装置10生成波形函数13,该波形函数13利用以第一参数为系数的多项式14定义脉冲信号上升时间第一区间内的幅度时间变化,并利用以第二参数为系数的多项式15定义脉冲信号上升时间第二区间内的幅度时间变化。信息处理装置10通过在参数组中设置参数值组16,利用波形函数13确定波形17。基于量子计算机利用具有波形17的脉冲信号进行量子计算的结果,信息处理装置10将参数组中设置的参数值组从参数值组16更改为参数值组18。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=606618bf-4f37-44d1-babb-5c7285a48bed&amp;shareId=4B84F79D-414E-727D-271B-84EBE715CCCG&amp;from=EXPORT&amp;signature=arZXB8CEMg6SAGFUbnrUeOsOJMNFDKw%2FOkBX%2FTXfk14%3D&amp;expire=94608000&amp;date=20260717T010927Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=0471384c-1a2f-4864-95d1-c6ca25e01ebd&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=dFq5ZPyNUtI0g9URJzDMdDaCYYIldaOnQjzSHtQmL%2FQ%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>一种用于量子芯片的参数校准方法及系统</t>
+          <t>量子门校准程序、量子门校准方法和信息处理装置。</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>量子科技长三角产业创新中心 | 中电科国基量子产业(苏州)有限公司</t>
+          <t>富士通株式会社</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>陈玉光 | 王碧莹</t>
+          <t>杉山 太香典</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -661,17 +662,55 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>本公开提供了一种用于量子芯片的参数校准方法及系统，方法包括获取校准的原始数据；对原始数据进行第一层级评估，若数据质量不满足标准则执行第一重试策略，调整硬件参数重新获取数据；若满足标准则对中间分析结果进行第二层级评估，若结果不满足标准则判定失效类型；若为实验参数失配则执行第一重试策略，若为算法失配则执行第二重试策略调整算法；当双重评估均通过时输出最终校准参数，校准方法将输出参数应用于量子芯片。本公开通过双重评估与两级重试，提升校准成功率与准确性。</t>
+          <t>为了提高量子门的校准精度。 
+ 【解决方案】信息处理装置 10 获取误差数据 14,该数据表明量子门 13a 存在误差。信息处理装置 10 使用近似函数 15 线性近似附加量子门对量子门 13a 运行的影响,从而生成包含与附加量子门对应的变量的线性方程 16,该方程表示附加量子门如何抵消误差。信息处理装置 10 通过求解线性方程 16 中的变量来确定与附加量子门对应的量子门 13b。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=5b6aca0e-9969-4dc7-b092-f307debaa46f&amp;shareId=4B84F79D-414E-727D-271B-84EBE715CCCG&amp;from=EXPORT&amp;signature=Ea9Lvu%2FeM1ETiEb99IcYydgn%2BOXuVZw7MzJIfsP6N58%3D&amp;expire=94608000&amp;date=20260717T010927Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=8557ce7e-4336-463b-b312-c5870cab6e17&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=TWaxFObGDY2vKIfmffzy%2FsGS6Hv%2F%2FOhFuwBTvWIogxg%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>利用莫尔超晶格的横向光驱动混合激子量子比特器件</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INTELLECTURE FUTURE IP MANAGEMENT CO LTD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>안범주</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>本发明涉及一种基于莫尔超晶格的横向光驱动混合激子量子比特器件,其包括:基于莫尔超晶格的量子信息层,其中第一二维半导体层和第二二维半导体层以一定扭转角堆叠,自然形成周期性势阱;光生层,用于从侧面入射控制光;静电门部分,用于主动控制势阱;以及光电探测器层,用于探测发射光。通过混合结合莫尔超晶格的物理限制和静电门部分的电学控制,本发明提供了以下功能:形成大面积均匀量子比特阵列、单个量子比特的选择控制、基于扭转角的势阱优化、通过密度梯度加速激子扩散、通过横向光入射消除栅极线路干扰以及基于谷自由度的量子比特初始化。</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=7e36bf39-715f-47e9-9c8b-9afce40699c2&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=k0p30DV4VSL%2BjBZHCIJ6DGQtR5jlGDs%2B1%2BBH2hIiZYQ%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_超导量子测控技术.xlsx
+++ b/weekly_temp/patents_超导量子测控技术.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,54 +456,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>量子处理系统</t>
+          <t>利用超导刚挠性电路在量子比特表面和量子比特表面控制系统之间维持高热梯度的系统和方法。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>硅量子计算私人有限公司</t>
+          <t>微软技术许可有限责任公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SIMMONS, MICHELLE YVONNE | HOUSE, MATTHEW GREGORY | GORMAN, SAMUEL KEITH | HOGG, MARK RICHARD</t>
+          <t>ターナー,マシュー デイビッド | ランタ,クレイグ スティーブン | クレイマー,ケビン ジェームス</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本公开涉及量子处理系统,该系统包括位于半导体衬底上的多个供体原子量子比特。该系统还包括多个用于控制供体原子量子比特的控制门。该系统还包括制造在半导体衬底上/内部的超晶格量子点(SLQD)电荷传感器。该SLQD电荷传感器用于检测位于其检测范围内的两个或多个供体原子量子比特的自旋态。</t>
+          <t>本文描述了一种用于在量子比特表面和量子比特表面控制系统之间维持高热梯度的系统和方法。该系统包括与超导刚挠性电路的第一刚性电路部分关联的量子比特表面,以及与该超导刚挠性电路的第二刚性电路部分关联的控制系统。该超导刚挠性电路包括用于连接第一刚性电路部分和第二刚性电路部分的柔性电路部分。该系统还包括第一冷却系统,其能够将量子比特表面和超导刚挠性电路的第一刚性电路部分的工作温度维持在100毫开尔文以下。该系统还包括控制系统和第二冷却系统,其能够将超导刚挠性电路的第二刚性电路部分的工作温度维持在10开尔文以下。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=de02e88f-ab34-41f9-bdca-1d6f631500dc&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=8uajQVCH%2BY1pHEWnSER4rQjXx9lvEeJ%2BHGdWgSQE5ls%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=f09696bb-8816-4864-a2c1-3f0831f74505&amp;shareId=07BG8958-DG59-7CG7-CG97-9010C6F472GB&amp;from=EXPORT&amp;signature=anTs3q%2B3y0ErX5vYQ2ejc94CCYrVY03gELPlewhSe78%3D&amp;expire=94608000&amp;date=20260828T063251Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>量子比特的加性控制实现了时域和频域复用。</t>
+          <t>一种多比特可扩展量子测控系统</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IQM芬兰有限公司</t>
+          <t>成都中微达信科技有限公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ヘインスー ヨハネス</t>
+          <t>邹小波 | 林海川 | 曾耿华 | 王渊</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,34 +513,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>该量子电子电路包括量子电路元件 (101)、控制信号线 (102, 103) 以及位于控制信号线 (102, 103) 和量子电路元件 (101) 之间的信号耦合单元,用于将至少部分控制信号线 (102, 103) 耦合到至少部分量子电路元件 (101)。控制信号线至少分为第一子集 (102) 和第二子集 (103)。信号耦合单元将至少一个子组中的每个量子电路元件 (101) 分别耦合到第一子集 (102) 和第二子集 (103) 的相应控制信号线。这样,子组中各个量子电路元件 (101) 的状态就可以通过分别经由第一子集 (102) 和第二子集 (103) 的相应控制信号线传输的加性控制信号进行加性控制。</t>
+          <t>本发明公开了一种多比特可扩展量子测控系统，在该系统中，量子测控单元、时钟分发单元和触发分发单元均可根据需要测量与控制的量子比特数量进行相应扩展，并通过数据传输网络与上位机进行通信交互，实现量子测控的相关工作；由于量子测控单元的时钟信号和触发信号由时钟分发单元和触发分发单元提供，且时钟分发单元和触发分发由于均是一路输入多路输出，能够通过级联实现大规模的扩展。因此，本发明通过单独地设置时钟分发单元和触发分发单元来为众多的量子测控单元提供时钟信号和触发信号，能够使同步性更加稳定，可提高量子测控的保真度，适用于大规模量子比特扩展的量子测控场景。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=8bb19c6f-53e7-456b-abb8-fe646424e372&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=9ZlsJJzic0eXWeJSC7DzdTnAExam%2BdZ7MQetjlKJeVc%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=70d3a2af-0890-42d6-871b-abd15755d8e3&amp;shareId=07BG8958-DG59-7CG7-CG97-9010C6F472GB&amp;from=EXPORT&amp;signature=QDn%2BZBN3fM4gIUDAHzIVU68Ln40%2Fh6n0Tp3NcLUvAR0%3D&amp;expire=94608000&amp;date=20260828T063251Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>波形处理方法、测控系统、量子计算机、介质和设备</t>
+          <t>内外部时钟信号自动切换电路、超导量子比特测控系统及其发射单元和量子计算装置</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>本源量子计算科技(合肥)股份有限公司</t>
+          <t>深圳量旋科技有限公司</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>请求不公布姓名 | 孔伟成</t>
+          <t>俞圣 | 邹宏洋</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -550,71 +550,71 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>本申请提供了波形处理方法、测控系统、量子计算机、介质和设备，所述方法包括：接收传输波形指令和扫描数据；使用所述扫描数据处理所述传输波形指令，以得到多个输出波形指令；将所述输出波形指令编译成实际波形数据，所述实际波形数据用于在量子计算测控实验任务中对量子比特进行控制或者测量。本申请允许对扫描数据与传输波形指令进行分离传输处理，实现内存的压缩，在编译过程中，所占用的内存较少，能够显著改善内存不足问题，降低任务失败风险，促进量子计算测控实验任务顺利完成，简化波形拼接等操作，允许用户更自由、灵活地去定义实验过程，不仅压缩量子计算测控实验的传输数据量，还有利于解耦实验和硬件，实现跨平台的兼容性。</t>
+          <t>本发明公开了一种内外部时钟信号自动切换电路、超导量子比特测控系统及其发射单元和量子计算装置。所述内外部时钟信号自动切换电路包括：时钟信号检测电路和通道开关芯片；时钟信号检测电路检测是否有接入外部时钟信号，若检测到接入，将外部时钟信号转换成第一电压信号，将第一电压信号转换成光能并将光电耦合得到的第一控制信号输出给通道开关芯片；反之，将第二控制信号输出给通道开关芯片；通道开关芯片根据输入的第一控制信号或第二控制信号，在两个时钟信号通道之间进行切换，输出对应的内部时钟信号或者外部时钟信号。本发明将输入的内外部时钟信号有可能的干扰噪声隔断在前端，避免了对系统时钟信号的干扰，保证了系统时钟信号的质量。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=04421a75-2c47-4bb8-ab9e-d0027df4377f&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=586qTljgnHyuxvIWxVfqucItJIHechPYEqTjnLxKvMI%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=dd269058-c73f-4de7-9b32-997c2dad1a02&amp;shareId=07BG8958-DG59-7CG7-CG97-9010C6F472GB&amp;from=EXPORT&amp;signature=YUDyY0AplfcPWKZVsKOItJlzH5LAKR8sHHUo603aciE%3D&amp;expire=94608000&amp;date=20260828T063251Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>针对延展十字码的稳定子测量方法、装置、设备及存储介质</t>
+          <t>一种扩展量子测控AWG数据波形长度的方法</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>成都中微达信科技有限公司</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>陈建鑫 | 周润石</t>
+          <t>于海 | 张子墨 | 黄守伟 | 吴方</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>本申请提供一种针对延展十字码的稳定子测量方法、装置、设备及存储介质，在症状提取周期的第一处理阶段，将X辅助量子比特与数据量子比特Ak+1执行CNOT门；从数据量子比特Ak到数据量子比特Am+1，依次与X辅助量子比特执行目标双比特门；将Z辅助量子比特与数据量子比特执行CNOT门；从数据量子比特到数据量子比特Am，依次与Z辅助量子比特执行目标双比特门；在第二处理阶段，将目标辅助量子比特与数据量子比特执行CNOT门；控制数据量子比特至数据量子比特Bk，依次与目标辅助量子比特执行目标双比特门；将目标辅助量子比特与数据量子比特Bk+1执行CNOT门；在第三处理阶段后，确定延展十字码中X稳定子和Z稳定子的测量数据。</t>
+          <t>本发明公开了一种扩展量子测控AWG数据波形长度的方法，涉及超导量子计算测控技术领域，步骤1，确定目标频率、采样率、带通滤波器参数及原始存储深度；步骤2，按目标频率与采样率比值选内插模式，基础采样率为目标的1/2；步骤3，用DDS生成脉冲样点，14bit有效数据16bit存储，CRC校验并加窗抑制旁瓣；步骤4，低延迟内插扩展样点至2倍，延迟≤5ns；步骤5，DAC开MIX模式，触发同步，串联滤波器滤镜像；步骤6，验证时长、功率与失真度，不达标则调整。本发明无额外硬件成本，低延迟适配量子反馈，AWG波形时长翻倍，信号质量好，兼容多采样率与频率范围，FPGA资源开销小，适配长寿命量子芯片。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=a6acd9eb-0c6f-440e-bf4f-ff1268703a36&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=oGaZ0B49phirzh6bOJFN43KfkVkzyQh7YVhU5Qf9g2Q%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=24645002-e82f-4cb4-afef-736d32a16b41&amp;shareId=07BG8958-DG59-7CG7-CG97-9010C6F472GB&amp;from=EXPORT&amp;signature=YO46TUfj%2BV9op851QovUYQSMum7J0Oh658Cp1AfqjVc%3D&amp;expire=94608000&amp;date=20260828T063251Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>量子比特控制程序、量子比特控制方法和信息处理装置。</t>
+          <t>一种量子脉冲控制方法、装置及电子设备和存储介质</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>富士通株式会社</t>
+          <t>深圳量旋科技有限公司</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>阿部 徹 | 杉山 太香典</t>
+          <t>叶惺 | 孟铁军</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,35 +624,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>减小用于控制量子比特的脉冲信号的参数。 
- 【解决方案】信息处理装置10生成波形函数13,该波形函数13利用以第一参数为系数的多项式14定义脉冲信号上升时间第一区间内的幅度时间变化,并利用以第二参数为系数的多项式15定义脉冲信号上升时间第二区间内的幅度时间变化。信息处理装置10通过在参数组中设置参数值组16,利用波形函数13确定波形17。基于量子计算机利用具有波形17的脉冲信号进行量子计算的结果,信息处理装置10将参数组中设置的参数值组从参数值组16更改为参数值组18。</t>
+          <t>本申请公开了一种量子脉冲控制方法、装置及设备和存储介质，应用于控制器，该方法包括：获取量子测控任务中每个脉冲通道的脉冲时间长度，并获取可编程逻辑器件中每个缓存通道的最大缓存脉冲时间长度；根据各脉冲通道的脉冲时间长度与各缓存通道的最大缓存脉冲时间长度生成资源分配表，资源分配表用于描述每个脉冲通道的脉冲波形数据与至少一个缓存通道之间的缓存映射关系；将资源分配表与各脉冲通道的脉冲波形数据发送至可编程逻辑器件，以使可编程逻辑器件根据缓存映射关系将各脉冲通道的脉冲波形数据存储至对应的缓存通道。本申请在不改变硬件资源的前提下，提高了可编程逻辑器件内部的缓存资源利用率，满足更长退相干时间的量子比特操控需求。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=0471384c-1a2f-4864-95d1-c6ca25e01ebd&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=dFq5ZPyNUtI0g9URJzDMdDaCYYIldaOnQjzSHtQmL%2FQ%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=c5ad60c5-c773-4997-9155-8ab5d08724c6&amp;shareId=07BG8958-DG59-7CG7-CG97-9010C6F472GB&amp;from=EXPORT&amp;signature=D%2FPO%2B4bnkjva0W9VZ5dMQYNt%2FMa1Q2uRTYnD7xoR7oc%3D&amp;expire=94608000&amp;date=20260828T063251Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>量子门校准程序、量子门校准方法和信息处理装置。</t>
+          <t>能级差估计程序、能级差估计方法和量子计算系统</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>富士通株式会社</t>
+          <t>富士通株式会社 | 株式会社QUNASYS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杉山 太香典</t>
+          <t>松本 徳文 | 中川 裕也 | 日▲高▼ 裕一朗</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -662,35 +661,35 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>为了提高量子门的校准精度。 
- 【解决方案】信息处理装置 10 获取误差数据 14,该数据表明量子门 13a 存在误差。信息处理装置 10 使用近似函数 15 线性近似附加量子门对量子门 13a 运行的影响,从而生成包含与附加量子门对应的变量的线性方程 16,该方程表示附加量子门如何抵消误差。信息处理装置 10 通过求解线性方程 16 中的变量来确定与附加量子门对应的量子门 13b。</t>
+          <t>降低量子电路的深度。 
+ 【解决方案】处理单元 12 使量子计算机 20 执行量子电路 30。量子电路 30 包括第一极性的第一控制门 32 和第二极性的第二控制门 33,每个控制门均由一个辅助量子比特控制。第一控制门 32 将对应于哈密顿量 H(λ) 的第一时间演化算符应用于对应于量子态 |ψ&gt; 的一组量子比特。第二控制门 33 将对应于 H(λ+δλ) 的第二时间演化算符应用于同一组量子比特。处理单元 12 从量子计算机 20 获取一个概率振幅,该概率振幅对应于将两种时间演化算符应用于量子态 |ψ&gt; 的结果匹配 |ψ&gt; 的事件。处理单元 12 通过使用概率幅值执行离散傅里叶变换来获得 H(λ) 和 H(λ+δλ) 能级差的累积分布函数 40,并根据累积分布函数 40 估计差值。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=8557ce7e-4336-463b-b312-c5870cab6e17&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=TWaxFObGDY2vKIfmffzy%2FsGS6Hv%2F%2FOhFuwBTvWIogxg%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=61ae8ba9-7294-4370-a665-68e2d8b45361&amp;shareId=07BG8958-DG59-7CG7-CG97-9010C6F472GB&amp;from=EXPORT&amp;signature=gmfKAcYqhjVbj2Qu3jfqWEHTdmajQqeaALg3yRrKqec%3D&amp;expire=94608000&amp;date=20260828T063251Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>利用莫尔超晶格的横向光驱动混合激子量子比特器件</t>
+          <t>应用于量子态的量子门的控制哈密顿量</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INTELLECTURE FUTURE IP MANAGEMENT CO LTD</t>
+          <t>아이디어드 에스엘</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>안범주</t>
+          <t>알바레다 피케르, 기예르모 | 브라콘스 아스파치스, 마리오나 | 센티스 에레라, 가엘 | 라모스 베니테스, 헤수스 라몬 | 우르젤 우예, 누리아 | 알시나 코위, 마르크 | 루비오 준코사, 마르셀</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -700,17 +699,54 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>本发明涉及一种基于莫尔超晶格的横向光驱动混合激子量子比特器件,其包括:基于莫尔超晶格的量子信息层,其中第一二维半导体层和第二二维半导体层以一定扭转角堆叠,自然形成周期性势阱;光生层,用于从侧面入射控制光;静电门部分,用于主动控制势阱;以及光电探测器层,用于探测发射光。通过混合结合莫尔超晶格的物理限制和静电门部分的电学控制,本发明提供了以下功能:形成大面积均匀量子比特阵列、单个量子比特的选择控制、基于扭转角的势阱优化、通过密度梯度加速激子扩散、通过横向光入射消除栅极线路干扰以及基于谷自由度的量子比特初始化。</t>
+          <t>本发明提供了一种计算机实现的方法,用于确定应用于至少一个量子态的量子门 G 的控制哈密顿量。本发明还提供了根据所述控制哈密顿量驱动的量子系统。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=7e36bf39-715f-47e9-9c8b-9afce40699c2&amp;shareId=2D964960-7634-8196-BCGG-7CC863B10775&amp;from=EXPORT&amp;signature=k0p30DV4VSL%2BjBZHCIJ6DGQtR5jlGDs%2B1%2BBH2hIiZYQ%3D&amp;expire=94608000&amp;date=20260821T055342Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=5396a2c5-5e4b-4c72-90a2-49030502cf58&amp;shareId=07BG8958-DG59-7CG7-CG97-9010C6F472GB&amp;from=EXPORT&amp;signature=cv7eRuYKKE5BhXDnEUYDhGNQV8%2BY4JxOsDCTlTSlBgQ%3D&amp;expire=94608000&amp;date=20260828T063251Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>具有交替布局和屏蔽门的量子点器件</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>英特尔公司</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GEORGE, HUBERT C. | PILLARISETTY, RAVI | CLARKE, JAMES S.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>本发明公开了一种量子点器件,其具有与单行有源量子比特关联的交替排列的读取器件,并且可选地,还具有一个或多个屏蔽门。一种具有交替排列布局的量子点器件示例包括:位于有源量子比特行一侧、靠近有源量子比特行第一部分的第一读取器件,用于检测/读取有源量子比特行第一子集的量子态;以及位于有源量子比特行另一侧、靠近有源量子比特行第二部分的第二读取器件,用于检测/读取有源量子比特行第二子集的量子态。屏蔽门可以设置在与读取器件和有源量子比特行耦合的各个门之间,以控制有源量子比特行的量子比特与读取器件之间以及不同读取器件之间的静电相互作用。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=07e58803-234c-4724-a0bb-dec439b04b41&amp;shareId=07BG8958-DG59-7CG7-CG97-9010C6F472GB&amp;from=EXPORT&amp;signature=N9RJceluh1tsmZDIufqUg60CPoz0TTVJ%2BdjaVNIqhYo%3D&amp;expire=94608000&amp;date=20260828T063251Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
